--- a/Passwords - Events.xlsx
+++ b/Passwords - Events.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="82">
   <si>
     <t>tpsa@rediffmail.com</t>
   </si>
@@ -331,25 +331,13 @@
     <t>git clone https://github.com/tpsarora/jagjitwelfare.git</t>
   </si>
   <si>
-    <t>tavinderevent@gmail.com</t>
-  </si>
-  <si>
-    <t>Jagjeetkaur2014@gmail.com</t>
-  </si>
-  <si>
     <t>malikaarora12345@gmail.com</t>
   </si>
   <si>
     <t>malika12345</t>
   </si>
   <si>
-    <t>template_68lymbm</t>
-  </si>
-  <si>
     <t>Template ID</t>
-  </si>
-  <si>
-    <t>service_ql34eml</t>
   </si>
   <si>
     <t>Service_ID</t>
@@ -517,13 +505,55 @@
   </si>
   <si>
     <t>Malikaarora12345@gmail.com</t>
+  </si>
+  <si>
+    <t>        // Initialize EmailJS</t>
+  </si>
+  <si>
+    <t>        emailjs.init("UUiVKSDERxZLzZndq");</t>
+  </si>
+  <si>
+    <t>            })</t>
+  </si>
+  <si>
+    <t> function sendEmail(toEmail, subject, message, name, link) {</t>
+  </si>
+  <si>
+    <t>            emailjs.send("service_ql34eml", "template_68lymbm", {</t>
+  </si>
+  <si>
+    <t>                to_name: name,</t>
+  </si>
+  <si>
+    <t>                subject: subject,</t>
+  </si>
+  <si>
+    <t>                message: message,</t>
+  </si>
+  <si>
+    <t>                email: toEmail,</t>
+  </si>
+  <si>
+    <t>                link: link</t>
+  </si>
+  <si>
+    <t>service_jitwsrj</t>
+  </si>
+  <si>
+    <t>template_8wpg95p</t>
+  </si>
+  <si>
+    <t>UUiVKSDERxZLzZndq</t>
+  </si>
+  <si>
+    <t>Public Key</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -609,6 +639,19 @@
       <color rgb="FF146C2E"/>
       <name val="Google Sans Code"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -630,7 +673,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -638,12 +681,103 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -675,11 +809,50 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -953,7 +1126,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1337,139 +1510,180 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.28515625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="37.28515625" style="15" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" ht="30.75" thickBot="1">
+      <c r="A1" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="30">
+        <v>9810607799</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A2" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="27" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="15" t="s">
+    <row r="4" spans="1:9">
+      <c r="A4" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="18"/>
+      <c r="B5" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="I5" s="21" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="18"/>
+      <c r="B6" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C6" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="18"/>
+      <c r="B7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="C3">
-        <v>9810607799</v>
-      </c>
-      <c r="H3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" t="s">
+      <c r="C7" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="I7" s="21" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="I8" s="21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="I9" s="21" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="I10" s="21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="I11" s="21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="B8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
+      <c r="I13" s="21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="I14" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" t="s">
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="16" t="s">
+    <row r="23" spans="1:1">
+      <c r="A23" s="17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="17" t="s">
+    <row r="25" spans="1:1">
+      <c r="A25" s="17" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="17" t="s">
+    <row r="27" spans="1:1">
+      <c r="A27" s="17" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="17" t="s">
+    <row r="29" spans="1:1">
+      <c r="A29" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="17" t="s">
+    <row r="31" spans="1:1">
+      <c r="A31" s="17" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="17" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="17" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:A7"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1"/>
-    <hyperlink ref="B1" r:id="rId2"/>
-    <hyperlink ref="A35" r:id="rId3"/>
-    <hyperlink ref="B35" r:id="rId4"/>
+    <hyperlink ref="B2" r:id="rId1"/>
+    <hyperlink ref="C2" r:id="rId2"/>
+    <hyperlink ref="B4" r:id="rId3"/>
+    <hyperlink ref="C4" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId5"/>

--- a/Passwords - Events.xlsx
+++ b/Passwords - Events.xlsx
@@ -553,7 +553,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -645,13 +645,6 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -818,9 +811,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -844,14 +834,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1126,7 +1119,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1520,92 +1513,92 @@
     <col min="5" max="16384" width="9.140625" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30.75" thickBot="1">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1">
+      <c r="A1" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C1" s="30">
+      <c r="C1" s="28">
         <v>9810607799</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="26" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="29"/>
+      <c r="B5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="I5" s="20" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="18"/>
-      <c r="B6" s="20" t="s">
+      <c r="A6" s="29"/>
+      <c r="B6" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="20" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="18"/>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="29"/>
+      <c r="B7" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="20" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="20" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="I9" s="21" t="s">
+      <c r="I9" s="20" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="I10" s="21" t="s">
+      <c r="I10" s="20" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="I11" s="21" t="s">
+      <c r="I11" s="20" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1613,7 +1606,7 @@
       <c r="A12" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="21" t="s">
+      <c r="I12" s="20" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1621,12 +1614,12 @@
       <c r="A13" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I13" s="20" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="20" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1684,8 +1677,9 @@
     <hyperlink ref="C2" r:id="rId2"/>
     <hyperlink ref="B4" r:id="rId3"/>
     <hyperlink ref="C4" r:id="rId4"/>
+    <hyperlink ref="A1" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
+  <pageSetup orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/Passwords - Events.xlsx
+++ b/Passwords - Events.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="82">
   <si>
     <t>tpsa@rediffmail.com</t>
   </si>
@@ -770,7 +770,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -840,11 +840,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1119,7 +1122,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1514,7 +1517,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>52</v>
       </c>
       <c r="B1" s="27" t="s">
@@ -1536,7 +1539,7 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="30" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -1547,7 +1550,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="29"/>
+      <c r="A5" s="30"/>
       <c r="B5" s="18" t="s">
         <v>81</v>
       </c>
@@ -1559,7 +1562,7 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="29"/>
+      <c r="A6" s="30"/>
       <c r="B6" s="19" t="s">
         <v>54</v>
       </c>
@@ -1571,7 +1574,7 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="29"/>
+      <c r="A7" s="30"/>
       <c r="B7" s="19" t="s">
         <v>55</v>
       </c>
@@ -1606,12 +1609,15 @@
       <c r="A12" s="15" t="s">
         <v>56</v>
       </c>
+      <c r="B12" s="15" t="s">
+        <v>67</v>
+      </c>
       <c r="I12" s="20" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="31" t="s">
         <v>57</v>
       </c>
       <c r="I13" s="20" t="s">
@@ -1678,8 +1684,9 @@
     <hyperlink ref="B4" r:id="rId3"/>
     <hyperlink ref="C4" r:id="rId4"/>
     <hyperlink ref="A1" r:id="rId5"/>
+    <hyperlink ref="A13" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId6"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/Passwords - Events.xlsx
+++ b/Passwords - Events.xlsx
@@ -843,11 +843,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1122,7 +1122,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1539,7 +1539,7 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="31" t="s">
         <v>13</v>
       </c>
       <c r="B4" s="22" t="s">
@@ -1550,7 +1550,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="30"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="18" t="s">
         <v>81</v>
       </c>
@@ -1562,7 +1562,7 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="30"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="19" t="s">
         <v>54</v>
       </c>
@@ -1574,7 +1574,7 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="30"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="19" t="s">
         <v>55</v>
       </c>
@@ -1617,7 +1617,7 @@
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="30" t="s">
         <v>57</v>
       </c>
       <c r="I13" s="20" t="s">
